--- a/public/tests/data/test_prices_sheet.xlsx
+++ b/public/tests/data/test_prices_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF200D2-4707-4587-BA21-E076DE6A4E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF700063-DAEB-42D7-B019-1229C64DF6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>0 days</t>
+  </si>
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>Prices_A1</t>
   </si>
 </sst>
 </file>
@@ -577,26 +583,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_prices_sheet.xlsx
+++ b/public/tests/data/test_prices_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF700063-DAEB-42D7-B019-1229C64DF6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7BAA06-9F7C-42FF-9D69-E8B56EBF092F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -62,12 +62,6 @@
     <t>end</t>
   </si>
   <si>
-    <t>portfolios_source</t>
-  </si>
-  <si>
-    <t>assets_source</t>
-  </si>
-  <si>
     <t>Assets</t>
   </si>
   <si>
@@ -150,6 +144,12 @@
   </si>
   <si>
     <t>Prices_A1</t>
+  </si>
+  <si>
+    <t>portfolios</t>
+  </si>
+  <si>
+    <t>assets</t>
   </si>
 </sst>
 </file>
@@ -498,7 +498,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -536,18 +536,18 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -562,15 +562,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -591,24 +591,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -626,13 +626,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -1003,10 +1003,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -1280,18 +1280,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -1577,46 +1577,46 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2">
         <v>45658</v>
@@ -1625,10 +1625,10 @@
         <v>45689</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5">
         <v>31</v>
@@ -1643,7 +1643,7 @@
         <v>79.53</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K2" s="5">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
